--- a/crates/xlstream-eval/tests/fixtures/logical/iferror_ifna.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/logical/iferror_ifna.xlsx
@@ -21,21 +21,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="15">
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="13">
   <si>
     <t xml:space="preserve">val</t>
   </si>
   <si>
-    <t xml:space="preserve">region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iferror</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ifna</t>
+    <t xml:space="preserve">key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iferror_div</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iferror_ok</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ifna_found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ifna_missing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iferror_nested</t>
   </si>
   <si>
     <t xml:space="preserve">EMEA</t>
@@ -44,28 +50,16 @@
     <t xml:space="preserve">APAC</t>
   </si>
   <si>
+    <t xml:space="preserve">ZZZ</t>
+  </si>
+  <si>
     <t xml:space="preserve">AMER</t>
   </si>
   <si>
-    <t xml:space="preserve">Europe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Asia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Americas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LATAM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LatAm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MidEast</t>
+    <t xml:space="preserve">XXX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YYY</t>
   </si>
 </sst>
 </file>
@@ -338,7 +332,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -357,195 +351,235 @@
       <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="0" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="B2" s="0" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>5</v>
+      <c r="B2" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <f aca="false">IFERROR(10/A2,-1)</f>
+        <v>1</v>
       </c>
       <c r="D2" s="0" t="n">
-        <f aca="false">IFERROR(A2/B2,-1)</f>
-        <v>2.85714285714286</v>
-      </c>
-      <c r="E2" s="0" t="str">
-        <f aca="false">_xlfn.IFNA(VLOOKUP(C2,Lookup1!A:C,2,FALSE()),"missing")</f>
-        <v>Europe</v>
+        <f aca="false">IFERROR(A2+1,0)</f>
+        <v>11</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <f aca="false">_xlfn.IFNA(VLOOKUP(B2,Lookup1!A:B,2,FALSE()),"missing")</f>
+        <v>100</v>
+      </c>
+      <c r="F2" s="0" t="str">
+        <f aca="false">_xlfn.IFNA(VLOOKUP("NOPE",Lookup1!A:B,2,FALSE()),"missing")</f>
+        <v>missing</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <f aca="false">IFERROR(IFERROR(1/A2,-99)+1,0)</f>
+        <v>1.1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
-        <v>25</v>
-      </c>
-      <c r="B3" s="0" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <f aca="false">IFERROR(10/A3,-1)</f>
+        <v>-1</v>
       </c>
       <c r="D3" s="0" t="n">
-        <f aca="false">IFERROR(A3/B3,-1)</f>
-        <v>3.47222222222222</v>
-      </c>
-      <c r="E3" s="0" t="str">
-        <f aca="false">_xlfn.IFNA(VLOOKUP(C3,Lookup1!A:C,2,FALSE()),"missing")</f>
-        <v>Asia</v>
+        <f aca="false">IFERROR(A3+1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <f aca="false">_xlfn.IFNA(VLOOKUP(B3,Lookup1!A:B,2,FALSE()),"missing")</f>
+        <v>200</v>
+      </c>
+      <c r="F3" s="0" t="str">
+        <f aca="false">_xlfn.IFNA(VLOOKUP("NOPE",Lookup1!A:B,2,FALSE()),"missing")</f>
+        <v>missing</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <f aca="false">IFERROR(IFERROR(1/A3,-99)+1,0)</f>
+        <v>-98</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="B4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>7</v>
+        <v>5</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <f aca="false">IFERROR(10/A4,-1)</f>
+        <v>2</v>
       </c>
       <c r="D4" s="0" t="n">
-        <f aca="false">IFERROR(A4/B4,-1)</f>
-        <v>-1</v>
+        <f aca="false">IFERROR(A4+1,0)</f>
+        <v>6</v>
       </c>
       <c r="E4" s="0" t="str">
-        <f aca="false">_xlfn.IFNA(VLOOKUP(C4,Lookup1!A:C,2,FALSE()),"missing")</f>
-        <v>Americas</v>
+        <f aca="false">_xlfn.IFNA(VLOOKUP(B4,Lookup1!A:B,2,FALSE()),"missing")</f>
+        <v>missing</v>
+      </c>
+      <c r="F4" s="0" t="str">
+        <f aca="false">_xlfn.IFNA(VLOOKUP("NOPE",Lookup1!A:B,2,FALSE()),"missing")</f>
+        <v>missing</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <f aca="false">IFERROR(IFERROR(1/A4,-99)+1,0)</f>
+        <v>1.2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="n">
-        <v>100</v>
-      </c>
-      <c r="B5" s="0" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>5</v>
+        <v>20</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <f aca="false">IFERROR(10/A5,-1)</f>
+        <v>0.5</v>
       </c>
       <c r="D5" s="0" t="n">
-        <f aca="false">IFERROR(A5/B5,-1)</f>
-        <v>6.32911392405063</v>
-      </c>
-      <c r="E5" s="0" t="str">
-        <f aca="false">_xlfn.IFNA(VLOOKUP(C5,Lookup1!A:C,2,FALSE()),"missing")</f>
-        <v>Europe</v>
+        <f aca="false">IFERROR(A5+1,0)</f>
+        <v>21</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <f aca="false">_xlfn.IFNA(VLOOKUP(B5,Lookup1!A:B,2,FALSE()),"missing")</f>
+        <v>300</v>
+      </c>
+      <c r="F5" s="0" t="str">
+        <f aca="false">_xlfn.IFNA(VLOOKUP("NOPE",Lookup1!A:B,2,FALSE()),"missing")</f>
+        <v>missing</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <f aca="false">IFERROR(IFERROR(1/A5,-99)+1,0)</f>
+        <v>1.05</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="n">
-        <v>-5</v>
-      </c>
-      <c r="B6" s="0" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>6</v>
+        <v>-3</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <f aca="false">IFERROR(10/A6,-1)</f>
+        <v>-3.33333333333333</v>
       </c>
       <c r="D6" s="0" t="n">
-        <f aca="false">IFERROR(A6/B6,-1)</f>
-        <v>2.17391304347826</v>
+        <f aca="false">IFERROR(A6+1,0)</f>
+        <v>-2</v>
       </c>
       <c r="E6" s="0" t="str">
-        <f aca="false">_xlfn.IFNA(VLOOKUP(C6,Lookup1!A:C,2,FALSE()),"missing")</f>
-        <v>Asia</v>
+        <f aca="false">_xlfn.IFNA(VLOOKUP(B6,Lookup1!A:B,2,FALSE()),"missing")</f>
+        <v>missing</v>
+      </c>
+      <c r="F6" s="0" t="str">
+        <f aca="false">_xlfn.IFNA(VLOOKUP("NOPE",Lookup1!A:B,2,FALSE()),"missing")</f>
+        <v>missing</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <f aca="false">IFERROR(IFERROR(1/A6,-99)+1,0)</f>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="B7" s="0" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="C7" s="0" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="0" t="s">
         <v>7</v>
       </c>
+      <c r="C7" s="0" t="n">
+        <f aca="false">IFERROR(10/A7,-1)</f>
+        <v>0.1</v>
+      </c>
       <c r="D7" s="0" t="n">
-        <f aca="false">IFERROR(A7/B7,-1)</f>
-        <v>6.17283950617284</v>
-      </c>
-      <c r="E7" s="0" t="str">
-        <f aca="false">_xlfn.IFNA(VLOOKUP(C7,Lookup1!A:C,2,FALSE()),"missing")</f>
-        <v>Americas</v>
+        <f aca="false">IFERROR(A7+1,0)</f>
+        <v>101</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <f aca="false">_xlfn.IFNA(VLOOKUP(B7,Lookup1!A:B,2,FALSE()),"missing")</f>
+        <v>100</v>
+      </c>
+      <c r="F7" s="0" t="str">
+        <f aca="false">_xlfn.IFNA(VLOOKUP("NOPE",Lookup1!A:B,2,FALSE()),"missing")</f>
+        <v>missing</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <f aca="false">IFERROR(IFERROR(1/A7,-99)+1,0)</f>
+        <v>1.01</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
-        <v>75</v>
-      </c>
-      <c r="B8" s="0" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <f aca="false">IFERROR(10/A8,-1)</f>
+        <v>-1</v>
       </c>
       <c r="D8" s="0" t="n">
-        <f aca="false">IFERROR(A8/B8,-1)</f>
-        <v>16.304347826087</v>
+        <f aca="false">IFERROR(A8+1,0)</f>
+        <v>1</v>
       </c>
       <c r="E8" s="0" t="str">
-        <f aca="false">_xlfn.IFNA(VLOOKUP(C8,Lookup1!A:C,2,FALSE()),"missing")</f>
-        <v>Europe</v>
+        <f aca="false">_xlfn.IFNA(VLOOKUP(B8,Lookup1!A:B,2,FALSE()),"missing")</f>
+        <v>missing</v>
+      </c>
+      <c r="F8" s="0" t="str">
+        <f aca="false">_xlfn.IFNA(VLOOKUP("NOPE",Lookup1!A:B,2,FALSE()),"missing")</f>
+        <v>missing</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <f aca="false">IFERROR(IFERROR(1/A8,-99)+1,0)</f>
+        <v>-98</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="0" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>6</v>
+        <v>42</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <f aca="false">IFERROR(10/A9,-1)</f>
+        <v>0.238095238095238</v>
       </c>
       <c r="D9" s="0" t="n">
-        <f aca="false">IFERROR(A9/B9,-1)</f>
-        <v>2</v>
-      </c>
-      <c r="E9" s="0" t="str">
-        <f aca="false">_xlfn.IFNA(VLOOKUP(C9,Lookup1!A:C,2,FALSE()),"missing")</f>
-        <v>Asia</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
-        <v>999</v>
-      </c>
-      <c r="B10" s="0" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="0" t="n">
-        <f aca="false">IFERROR(A10/B10,-1)</f>
-        <v>80.5645161290323</v>
-      </c>
-      <c r="E10" s="0" t="str">
-        <f aca="false">_xlfn.IFNA(VLOOKUP(C10,Lookup1!A:C,2,FALSE()),"missing")</f>
-        <v>Americas</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
-        <v>42</v>
-      </c>
-      <c r="B11" s="0" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="0" t="n">
-        <f aca="false">IFERROR(A11/B11,-1)</f>
-        <v>6.26865671641791</v>
-      </c>
-      <c r="E11" s="0" t="str">
-        <f aca="false">_xlfn.IFNA(VLOOKUP(C11,Lookup1!A:C,2,FALSE()),"missing")</f>
-        <v>Europe</v>
+        <f aca="false">IFERROR(A9+1,0)</f>
+        <v>43</v>
+      </c>
+      <c r="E9" s="0" t="n">
+        <f aca="false">_xlfn.IFNA(VLOOKUP(B9,Lookup1!A:B,2,FALSE()),"missing")</f>
+        <v>200</v>
+      </c>
+      <c r="F9" s="0" t="str">
+        <f aca="false">_xlfn.IFNA(VLOOKUP("NOPE",Lookup1!A:B,2,FALSE()),"missing")</f>
+        <v>missing</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <f aca="false">IFERROR(IFERROR(1/A9,-99)+1,0)</f>
+        <v>1.02380952380952</v>
       </c>
     </row>
   </sheetData>
@@ -564,62 +598,39 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="0" t="n">
-        <v>200</v>
+        <v>7</v>
+      </c>
+      <c r="B2" s="0" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>300</v>
+        <v>8</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>200</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>75</v>
+        <v>10</v>
+      </c>
+      <c r="B4" s="0" t="n">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
